--- a/keywords.xlsx
+++ b/keywords.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$F$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,11 +30,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00FF0000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -64,7 +59,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -72,7 +67,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,12 +432,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="64" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="53" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="100" customWidth="1" min="6" max="6"/>
@@ -484,7 +478,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>595cc开元官网版下载</t>
+          <t>星空入口</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Lỗi: Không thể thực hiện tìm kiếm chi tiết</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -492,24 +491,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>595cc开元官网版下载app2026最新版下载v.{getone name="diy:bben" cacheid="1"/} 安卓版-2265安卓网</t>
+          <t>星空入口-星空入口官方最新版2026V{getone name="diy:bben" cacheid="1"/} 安卓版-2265安卓网</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>星空入口</t>
+          <t>ayx游戏app官方版</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62星空入口:星河秘境,62星空入口,穿越时空之门!_广东...</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>gd.huatu.com</t>
+          <t>Lỗi: Không thể tạo page mới</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -522,33 +516,14 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>kiayun登录入口登录</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hth网页版在线登录入口</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="FFFF0000"/>
-            </rPr>
-            <t>kiayun登录入口登录</t>
-          </r>
-          <r>
-            <t>官方版-kiayun登录入口登录2026...</t>
-          </r>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>yaoshengcai.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>近期发布</t>
+          <t>Lỗi: Không thể tạo page mới</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -561,28 +536,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>星空手机网页版</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>星空·体育中国综合</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="FFFF0000"/>
-            </rPr>
-            <t>星空手机网页版</t>
-          </r>
-          <r>
-            <t>入口:星空手机网页版入口全新上线,便捷体验尽在...</t>
-          </r>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>gd.huatu.com</t>
+          <t>Lỗi: Không thể tạo page mới</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -594,8 +555,53 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>星空官方app下载</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Lỗi: Không thể tạo page mới</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>开云足球</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lỗi: Không thể tạo page mới</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>米兰电竞</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Lỗi: Không thể tạo page mới</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/keywords.xlsx
+++ b/keywords.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,15 +432,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="53" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="100" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,130 +478,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>星空入口</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Lỗi: Không thể thực hiện tìm kiếm chi tiết</t>
+          <t>1155电子游戏官网入口</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>星空入口-星空入口官方最新版2026V{getone name="diy:bben" cacheid="1"/} 安卓版-2265安卓网</t>
-        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ayx游戏app官方版</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Lỗi: Không thể tạo page mới</t>
+          <t>17CC一起起草平台登录步骤</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>星空入口-星空入口官方最新版2026V{getone name="diy:bben" cacheid="1"/} 安卓版-2265安卓网</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>hth网页版在线登录入口</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lỗi: Không thể tạo page mới</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>kiayun登录入口登录官方版-kiayun登录入口登录2026最新版 v{getone name="diy:bben" cacheid="1"/} 安卓版-2265安卓网</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>星空·体育中国综合</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Lỗi: Không thể tạo page mới</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>星空手机网页版登录入口-星空手机网页版登录入口最新版V{getone name="diy:bben" cacheid="1"/} 安卓版-2265安卓网</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>星空官方app下载</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Lỗi: Không thể tạo page mới</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>开云足球</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Lỗi: Không thể tạo page mới</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>米兰电竞</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Lỗi: Không thể tạo page mới</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>7</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:F3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>